--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N33_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N33_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.18343136161232</v>
+        <v>11.242307596262</v>
       </c>
       <c r="D2" t="n">
-        <v>22.96226104064591</v>
+        <v>3.731367419104961</v>
       </c>
       <c r="E2" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F2" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.10697723260223</v>
+        <v>9.117383800297864</v>
       </c>
       <c r="D3" t="n">
-        <v>38.31903920288318</v>
+        <v>6.226843870468517</v>
       </c>
       <c r="E3" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F3" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.93202001498083</v>
+        <v>2.588953252434385</v>
       </c>
       <c r="D4" t="n">
-        <v>15.10679702631459</v>
+        <v>2.45485451677612</v>
       </c>
       <c r="E4" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F4" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.604686356149273</v>
+        <v>1.560761532874257</v>
       </c>
       <c r="D5" t="n">
-        <v>10.11187420807834</v>
+        <v>1.643179558812731</v>
       </c>
       <c r="E5" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F5" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.46583312999539</v>
+        <v>2.350697883624251</v>
       </c>
       <c r="D6" t="n">
-        <v>14.40966542944219</v>
+        <v>2.341570632284356</v>
       </c>
       <c r="E6" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F6" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.76127175250945</v>
+        <v>9.548706659782786</v>
       </c>
       <c r="D7" t="n">
-        <v>55.92860219541007</v>
+        <v>9.088397856754137</v>
       </c>
       <c r="E7" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F7" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.98592448033426</v>
+        <v>2.922712728054317</v>
       </c>
       <c r="D8" t="n">
-        <v>18.05436982360879</v>
+        <v>2.933835096336429</v>
       </c>
       <c r="E8" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F8" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.21950207090288</v>
+        <v>7.673169086521719</v>
       </c>
       <c r="D9" t="n">
-        <v>46.15984722351311</v>
+        <v>7.500975173820881</v>
       </c>
       <c r="E9" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F9" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.48123274256326</v>
+        <v>9.665700320666529</v>
       </c>
       <c r="D10" t="n">
-        <v>59.54419233679535</v>
+        <v>9.675931254729246</v>
       </c>
       <c r="E10" t="n">
-        <v>22.41131405268235</v>
+        <v>3.641838533560882</v>
       </c>
       <c r="F10" t="n">
-        <v>17.99893102225423</v>
+        <v>2.924826291116312</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
